--- a/data/trans_orig/Q45B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q45B-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2007</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>18312</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42777</t>
+          <t>43201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68604</t>
+          <t>69404</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50889</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81147</t>
+          <t>83486</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>474504</t>
+          <t>474602</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>488443</t>
+          <t>488045</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>395370</t>
+          <t>394928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>422043</t>
+          <t>421435</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>876757</t>
+          <t>875303</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>907112</t>
+          <t>907210</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32294</t>
+          <t>31925</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92180</t>
+          <t>92236</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>130601</t>
+          <t>130902</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>110141</t>
+          <t>111205</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>153874</t>
+          <t>155187</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>696592</t>
+          <t>695509</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>717974</t>
+          <t>717989</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>489682</t>
+          <t>488956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>527545</t>
+          <t>528636</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1196568</t>
+          <t>1194447</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1240901</t>
+          <t>1238761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19369</t>
+          <t>19349</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33025</t>
+          <t>32507</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59640</t>
+          <t>59093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41757</t>
+          <t>43542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70811</t>
+          <t>74125</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>616728</t>
+          <t>617232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>631386</t>
+          <t>630997</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>627471</t>
+          <t>626843</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>654654</t>
+          <t>653971</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1252582</t>
+          <t>1247716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1281274</t>
+          <t>1280346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -2100,97 +2100,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6127</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1953</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6849</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6768</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>6068</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14532</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33807</t>
+          <t>33901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42406</t>
+          <t>42692</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>504615</t>
+          <t>504426</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>516852</t>
+          <t>517105</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>478696</t>
+          <t>479466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>499170</t>
+          <t>498758</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>990325</t>
+          <t>989575</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1012968</t>
+          <t>1013052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -2556,97 +2556,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1889</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1924</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16533</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>24027</t>
+          <t>25144</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>372804</t>
+          <t>373348</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>384236</t>
+          <t>384155</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>387453</t>
+          <t>386352</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>400130</t>
+          <t>399702</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>766669</t>
+          <t>765552</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>783028</t>
+          <t>781890</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,62 +3047,62 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>1775</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1770</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>6222</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1775</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>5737</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>286743</t>
+          <t>286888</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>331435</t>
+          <t>331443</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>341055</t>
+          <t>341024</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>621916</t>
+          <t>621730</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>631896</t>
+          <t>632564</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -3468,97 +3468,97 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1822</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2202</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3581,97 +3581,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>2091</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1822</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>9612</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>2091</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>7117</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>8507</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6758</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>208061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>209883</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>326791</t>
+          <t>324296</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>537033</t>
+          <t>535284</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>33890</t>
+          <t>35520</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>41981</t>
+          <t>40685</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72690</t>
+          <t>71108</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>221465</t>
+          <t>222005</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>282271</t>
+          <t>284702</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>272474</t>
+          <t>274280</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>342837</t>
+          <t>343549</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3193555</t>
+          <t>3192980</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3227215</t>
+          <t>3226611</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3083760</t>
+          <t>3080756</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3145380</t>
+          <t>3144442</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6287720</t>
+          <t>6287354</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6363238</t>
+          <t>6360052</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2012</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11165</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>16695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>20304</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26860</t>
+          <t>26825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49424</t>
+          <t>50673</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37044</t>
+          <t>37136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66643</t>
+          <t>64439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>426526</t>
+          <t>426834</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>442475</t>
+          <t>442405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>372221</t>
+          <t>371559</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>396699</t>
+          <t>396417</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>804655</t>
+          <t>806864</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>834956</t>
+          <t>835799</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10584</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28572</t>
+          <t>27501</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29195</t>
+          <t>29469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14463</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34228</t>
+          <t>34529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>76563</t>
+          <t>75755</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>111655</t>
+          <t>110385</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>94629</t>
+          <t>96275</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>135848</t>
+          <t>137971</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>648960</t>
+          <t>649145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>668913</t>
+          <t>668931</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>478475</t>
+          <t>481037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>517477</t>
+          <t>517572</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1137605</t>
+          <t>1135071</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1180743</t>
+          <t>1181091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>11432</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10730</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30483</t>
+          <t>30631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38273</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66326</t>
+          <t>66095</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53725</t>
+          <t>54452</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86717</t>
+          <t>87542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>650444</t>
+          <t>650296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>668902</t>
+          <t>668488</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>634740</t>
+          <t>635723</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>664076</t>
+          <t>664091</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1296140</t>
+          <t>1294624</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1329374</t>
+          <t>1329339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12491</t>
+          <t>12811</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15798</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>27309</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15776</t>
+          <t>15097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38251</t>
+          <t>37623</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>28872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58048</t>
+          <t>55902</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>581247</t>
+          <t>582214</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>599817</t>
+          <t>600904</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>569777</t>
+          <t>568178</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>593308</t>
+          <t>593149</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1159410</t>
+          <t>1160120</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1188177</t>
+          <t>1188980</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,62 +6474,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5947</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>5602</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>419291</t>
+          <t>418931</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>428298</t>
+          <t>428295</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>430476</t>
+          <t>429321</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>442480</t>
+          <t>442464</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>853155</t>
+          <t>853896</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>867883</t>
+          <t>867969</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -6895,97 +6895,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2101</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>18280</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20460</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>301339</t>
+          <t>302280</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>335396</t>
+          <t>334822</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>349568</t>
+          <t>350095</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>641412</t>
+          <t>641933</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>657832</t>
+          <t>657207</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -7351,97 +7351,97 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2152</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>2141</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>16389</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>241381</t>
+          <t>240605</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>371197</t>
+          <t>371407</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>383470</t>
+          <t>383511</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>615982</t>
+          <t>615760</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>630129</t>
+          <t>630188</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>14022</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22600</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>45214</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>28391</t>
+          <t>28197</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>56160</t>
+          <t>56159</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>60775</t>
+          <t>61465</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>98094</t>
+          <t>100013</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>199460</t>
+          <t>200194</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>263049</t>
+          <t>260980</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>275538</t>
+          <t>274911</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>342120</t>
+          <t>345805</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3307100</t>
+          <t>3306381</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3345692</t>
+          <t>3346047</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3246987</t>
+          <t>3248968</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3313750</t>
+          <t>3313699</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6569184</t>
+          <t>6570313</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6643390</t>
+          <t>6646195</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2016</t>
+          <t>Población según si han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>858</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>12940</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30672</t>
+          <t>29460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36258</t>
+          <t>36483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -8724,12 +8724,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>404955</t>
+          <t>404294</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>414308</t>
+          <t>414303</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>364050</t>
+          <t>363656</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>381230</t>
+          <t>381215</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>772175</t>
+          <t>772689</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>792704</t>
+          <t>793306</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8502</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23402</t>
+          <t>23477</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30939</t>
+          <t>30425</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54305</t>
+          <t>54819</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>44478</t>
+          <t>43894</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72703</t>
+          <t>71819</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>564951</t>
+          <t>564876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>579851</t>
+          <t>579842</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>502118</t>
+          <t>500419</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>526868</t>
+          <t>527280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1071169</t>
+          <t>1072175</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1101245</t>
+          <t>1102089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9445,47 +9445,47 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8913</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>3676</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>930</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9044</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>3676</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>31210</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36396</t>
+          <t>36866</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>657101</t>
+          <t>656324</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>665147</t>
+          <t>665116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>621886</t>
+          <t>622836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>641325</t>
+          <t>641959</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1283221</t>
+          <t>1282741</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1303803</t>
+          <t>1304175</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>10856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26998</t>
+          <t>26458</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30619</t>
+          <t>32949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>634341</t>
+          <t>634109</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>614326</t>
+          <t>613751</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>633532</t>
+          <t>632654</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1254829</t>
+          <t>1252695</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1274210</t>
+          <t>1273878</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -10322,97 +10322,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2323</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2156</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>8110</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>2323</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8174</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>7721</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2323</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>7260</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10450,67 +10450,67 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>5752</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>12692</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>5752</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>2277</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>12602</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>5752</t>
-        </is>
-      </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12659</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>472936</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>475092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>479793</t>
+          <t>479779</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>492396</t>
+          <t>492431</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>954768</t>
+          <t>954807</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>967513</t>
+          <t>967483</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10813,62 +10813,62 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>4349</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>4832</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>915</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>941</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -11004,12 +11004,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>323051</t>
+          <t>323863</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>331781</t>
+          <t>331793</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>369587</t>
+          <t>370450</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>696698</t>
+          <t>696647</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>705547</t>
+          <t>705598</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11234,97 +11234,97 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1628</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2544</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>2089</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11347,97 +11347,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1628</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>2544</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>2089</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>254543</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>256171</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>396354</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>398898</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11510,12 +11510,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>652979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>655068</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>13252</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>31120</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>44154</t>
+          <t>43054</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>87569</t>
+          <t>87907</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>126045</t>
+          <t>126287</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>113955</t>
+          <t>115839</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>158730</t>
+          <t>161425</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3333318</t>
+          <t>3334937</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3358024</t>
+          <t>3357023</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3386030</t>
+          <t>3384644</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3427890</t>
+          <t>3426550</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6728692</t>
+          <t>6729097</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6778469</t>
+          <t>6776837</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q45B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q45B-Edad-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18312</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43201</t>
+          <t>43025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69404</t>
+          <t>69516</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>52997</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83486</t>
+          <t>82014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>474602</t>
+          <t>473762</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>488045</t>
+          <t>488286</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>394928</t>
+          <t>394944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>421435</t>
+          <t>421523</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>875303</t>
+          <t>875299</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>907210</t>
+          <t>905028</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>20046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31925</t>
+          <t>31983</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92236</t>
+          <t>93037</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>130902</t>
+          <t>131448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>111205</t>
+          <t>112779</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>155187</t>
+          <t>157877</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>695509</t>
+          <t>696167</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>717989</t>
+          <t>718354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>488956</t>
+          <t>489962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>528636</t>
+          <t>528899</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1194447</t>
+          <t>1193072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1238761</t>
+          <t>1239110</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11106</t>
+          <t>12487</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>19179</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32507</t>
+          <t>32710</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59093</t>
+          <t>60660</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43542</t>
+          <t>42098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74125</t>
+          <t>72184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>617232</t>
+          <t>616794</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>630997</t>
+          <t>630417</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>626843</t>
+          <t>627229</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>653971</t>
+          <t>655091</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1247716</t>
+          <t>1250368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1280346</t>
+          <t>1282027</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33901</t>
+          <t>34572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20364</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42692</t>
+          <t>42817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>504426</t>
+          <t>504624</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>517105</t>
+          <t>517095</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>479466</t>
+          <t>479382</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>498758</t>
+          <t>498513</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>989575</t>
+          <t>989750</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1013052</t>
+          <t>1013112</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>14470</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25144</t>
+          <t>25098</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>373348</t>
+          <t>372240</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>384155</t>
+          <t>384075</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>386352</t>
+          <t>387285</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>399702</t>
+          <t>400048</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>765552</t>
+          <t>765598</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>781890</t>
+          <t>782010</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>286888</t>
+          <t>286580</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>331443</t>
+          <t>331149</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>341024</t>
+          <t>341012</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>621730</t>
+          <t>621870</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>632564</t>
+          <t>631970</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9612</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>324296</t>
+          <t>326643</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>535284</t>
+          <t>536149</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20592</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>35532</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>40685</t>
+          <t>41649</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>71108</t>
+          <t>70841</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>222005</t>
+          <t>223995</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>284702</t>
+          <t>286479</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>274280</t>
+          <t>270478</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>343549</t>
+          <t>336891</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3192980</t>
+          <t>3194420</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3226611</t>
+          <t>3226769</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3080756</t>
+          <t>3079454</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3144442</t>
+          <t>3144532</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6287354</t>
+          <t>6294006</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6360052</t>
+          <t>6363882</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>27567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50673</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37136</t>
+          <t>36661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64439</t>
+          <t>64557</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>426834</t>
+          <t>425091</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>442405</t>
+          <t>441911</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>371559</t>
+          <t>370908</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>396417</t>
+          <t>396244</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>806864</t>
+          <t>804562</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>835799</t>
+          <t>834989</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27501</t>
+          <t>28268</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29469</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14467</t>
+          <t>14050</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34529</t>
+          <t>34917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75755</t>
+          <t>74761</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>110385</t>
+          <t>108753</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>96275</t>
+          <t>93832</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>137971</t>
+          <t>136454</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>649145</t>
+          <t>648227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>668931</t>
+          <t>669507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>481037</t>
+          <t>480055</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>517572</t>
+          <t>517887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1135071</t>
+          <t>1137306</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1181091</t>
+          <t>1180304</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11432</t>
+          <t>10730</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>12593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30631</t>
+          <t>30459</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>36442</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66095</t>
+          <t>63886</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54452</t>
+          <t>54927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87542</t>
+          <t>86826</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>650296</t>
+          <t>650468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>668488</t>
+          <t>668334</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>635723</t>
+          <t>637278</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>664091</t>
+          <t>666476</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1294624</t>
+          <t>1295393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1329339</t>
+          <t>1328187</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12811</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14877</t>
+          <t>14816</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27309</t>
+          <t>25814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15097</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37623</t>
+          <t>37536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28872</t>
+          <t>27957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55902</t>
+          <t>55243</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>582214</t>
+          <t>582871</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>600904</t>
+          <t>600575</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>568178</t>
+          <t>568241</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>593149</t>
+          <t>593153</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1160120</t>
+          <t>1160308</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1188980</t>
+          <t>1190171</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20036</t>
+          <t>19682</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>418931</t>
+          <t>418782</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>428295</t>
+          <t>428353</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>429321</t>
+          <t>429950</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>442464</t>
+          <t>441644</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>853896</t>
+          <t>854073</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>867969</t>
+          <t>868039</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18280</t>
+          <t>18186</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>21204</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>302280</t>
+          <t>301385</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>334822</t>
+          <t>334916</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>350095</t>
+          <t>350123</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>641933</t>
+          <t>640668</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>657207</t>
+          <t>656916</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16389</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19847</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>240605</t>
+          <t>239710</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>371407</t>
+          <t>371265</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>383511</t>
+          <t>383476</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>615760</t>
+          <t>616282</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>630188</t>
+          <t>630183</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>15788</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,82 +7822,82 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>32967</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>22554</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>45786</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>40183</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>28695</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>55071</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>32967</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>23368</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>45214</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>40183</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>28197</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>56159</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>61465</t>
+          <t>61565</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>100013</t>
+          <t>96528</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>200194</t>
+          <t>200743</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>260980</t>
+          <t>262413</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>274911</t>
+          <t>274648</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>345805</t>
+          <t>346383</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3306381</t>
+          <t>3307123</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3346047</t>
+          <t>3343884</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3248968</t>
+          <t>3249607</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3313699</t>
+          <t>3312732</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6570313</t>
+          <t>6570169</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6646195</t>
+          <t>6644153</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>859</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29460</t>
+          <t>30507</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36483</t>
+          <t>35827</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -8724,12 +8724,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>404294</t>
+          <t>405187</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>414303</t>
+          <t>414310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>363656</t>
+          <t>363295</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>381215</t>
+          <t>380310</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>772689</t>
+          <t>772599</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>793306</t>
+          <t>792646</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>23036</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30425</t>
+          <t>29831</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54819</t>
+          <t>54150</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43894</t>
+          <t>42866</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71819</t>
+          <t>71440</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>564876</t>
+          <t>565317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>579842</t>
+          <t>580205</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>500419</t>
+          <t>501664</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>527280</t>
+          <t>527334</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1072175</t>
+          <t>1073016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1102089</t>
+          <t>1103741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -9445,12 +9445,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>950</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>949</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>978</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9839</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>32059</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>36386</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>656324</t>
+          <t>656002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>665116</t>
+          <t>665185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>622836</t>
+          <t>621300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>641959</t>
+          <t>641356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1282741</t>
+          <t>1284201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1304175</t>
+          <t>1305246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26458</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>11748</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32949</t>
+          <t>30431</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>634109</t>
+          <t>634613</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>643858</t>
+          <t>643872</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>613751</t>
+          <t>613379</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>632654</t>
+          <t>632602</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1252695</t>
+          <t>1254540</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1273878</t>
+          <t>1274622</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -10470,12 +10470,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13794</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>479779</t>
+          <t>478733</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>492431</t>
+          <t>492376</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>954807</t>
+          <t>955824</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>967483</t>
+          <t>967486</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7770</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -11004,12 +11004,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>323863</t>
+          <t>322219</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>331793</t>
+          <t>331778</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>370450</t>
+          <t>369722</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>696647</t>
+          <t>696696</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>705598</t>
+          <t>705618</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11805</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>29426</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12947</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>20971</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>43054</t>
+          <t>40827</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>87907</t>
+          <t>86340</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>126287</t>
+          <t>126815</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>115839</t>
+          <t>115714</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>161425</t>
+          <t>162373</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3334937</t>
+          <t>3336730</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3357023</t>
+          <t>3357336</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3384644</t>
+          <t>3385728</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3426550</t>
+          <t>3426760</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6729097</t>
+          <t>6729561</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6776837</t>
+          <t>6778372</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
